--- a/static/images/ashesi_timetable.xlsx
+++ b/static/images/ashesi_timetable.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\COMPUTING\programming\squarespace\aiesec.ca-squarespace\static\images\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07F546B9-CC54-4EF1-8F5D-CB51619A572D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D18980FC-2142-403D-8D1D-04FEA0808936}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="87">
   <si>
     <t>Ashesi University — Weekly Timetable</t>
   </si>
@@ -246,12 +246,6 @@
     <t>backend(13:45-14:45)</t>
   </si>
   <si>
-    <t>piano practice(4:00- 4:30)</t>
-  </si>
-  <si>
-    <t>assignments(4:30-6:00)</t>
-  </si>
-  <si>
     <t>school related(10:30 - 11:30)</t>
   </si>
   <si>
@@ -262,6 +256,51 @@
   </si>
   <si>
     <t>school related(1 hour)</t>
+  </si>
+  <si>
+    <t>Saturday</t>
+  </si>
+  <si>
+    <t>Wash clothes(6:00-8:00)</t>
+  </si>
+  <si>
+    <t>Watch movies/series(8:00-10:00)</t>
+  </si>
+  <si>
+    <t>eat,rest(10:00-10:30)</t>
+  </si>
+  <si>
+    <t>project(1:00-3:00)</t>
+  </si>
+  <si>
+    <t>assignments(3:00-4:30)</t>
+  </si>
+  <si>
+    <t>Sunday</t>
+  </si>
+  <si>
+    <t>school(</t>
+  </si>
+  <si>
+    <t>Church(8:00-12:30)</t>
+  </si>
+  <si>
+    <t>sleep to 2)</t>
+  </si>
+  <si>
+    <t>school related(2-4)</t>
+  </si>
+  <si>
+    <t>project(4-6)</t>
+  </si>
+  <si>
+    <t>eat, rest, movie,)</t>
+  </si>
+  <si>
+    <t>finish up and prepare for the week)</t>
+  </si>
+  <si>
+    <t>another study session(4-5:30)</t>
   </si>
 </sst>
 </file>
@@ -382,7 +421,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -416,11 +455,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD3D1C7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -446,6 +494,33 @@
     <xf numFmtId="0" fontId="10" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="4" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -470,24 +545,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="4" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -791,34 +848,34 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="6" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-    </row>
-    <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="9" t="s">
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+    </row>
+    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-    </row>
-    <row r="3" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+    </row>
+    <row r="3" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -837,8 +894,14 @@
       <c r="F3" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="52" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G3" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="H3" s="15" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="52" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
@@ -855,10 +918,13 @@
         <v>65</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="52" customHeight="1" x14ac:dyDescent="0.35">
+        <v>69</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="52" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
@@ -875,10 +941,16 @@
         <v>11</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="52" customHeight="1" x14ac:dyDescent="0.35">
+        <v>70</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="52" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
@@ -897,8 +969,14 @@
       <c r="F6" s="5" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" ht="52" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G6" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="H6" s="10" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="52" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>14</v>
       </c>
@@ -917,8 +995,14 @@
       <c r="F7" s="3" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" ht="52" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G7" t="s">
+        <v>79</v>
+      </c>
+      <c r="H7" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="52" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>17</v>
       </c>
@@ -937,8 +1021,14 @@
       <c r="F8" s="6" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" ht="52" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G8" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="52" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>19</v>
       </c>
@@ -955,10 +1045,16 @@
         <v>67</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="52" customHeight="1" x14ac:dyDescent="0.35">
+        <v>71</v>
+      </c>
+      <c r="G9" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="H9" s="12" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="52" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>21</v>
       </c>
@@ -975,8 +1071,11 @@
         <v>59</v>
       </c>
       <c r="F10" s="3"/>
-    </row>
-    <row r="11" spans="1:6" ht="52" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H10" s="12" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="52" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>23</v>
       </c>
@@ -992,7 +1091,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="52" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" ht="52" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>25</v>
       </c>
@@ -1006,135 +1105,133 @@
         <v>26</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="52" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="18" t="s">
+    <row r="13" spans="1:8" ht="52" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="20" t="s">
+      <c r="B13" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="C13" s="21" t="s">
+      <c r="C13" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="D13" s="22" t="s">
+      <c r="D13" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="E13" s="21" t="s">
-        <v>69</v>
-      </c>
-      <c r="F13" s="21" t="s">
+      <c r="E13" s="12"/>
+      <c r="F13" s="12" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="52" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="18" t="s">
+    <row r="14" spans="1:8" ht="52" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="20" t="s">
+      <c r="B14" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="C14" s="21" t="s">
+      <c r="C14" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="D14" s="22" t="s">
+      <c r="D14" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="E14" s="21" t="s">
+      <c r="E14" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="F14" s="21" t="s">
+      <c r="F14" s="12" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="52" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="23" t="s">
+    <row r="15" spans="1:8" ht="52" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="20" t="s">
+      <c r="B15" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="C15" s="21" t="s">
+      <c r="C15" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="D15" s="22" t="s">
+      <c r="D15" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="E15" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="F15" s="21" t="s">
+      <c r="E15" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="F15" s="12" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="18"/>
-      <c r="B16" s="19"/>
+    <row r="16" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="9"/>
+      <c r="B16" s="10"/>
     </row>
     <row r="17" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="13" t="s">
+      <c r="A17" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="B17" s="10"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="19"/>
     </row>
     <row r="18" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="17" t="s">
+      <c r="A18" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="B18" s="10"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="10"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="10"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="19"/>
     </row>
     <row r="19" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="11" t="s">
+      <c r="A19" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="B19" s="10"/>
-      <c r="C19" s="10"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="10"/>
-      <c r="F19" s="10"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="19"/>
     </row>
     <row r="20" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="15" t="s">
+      <c r="A20" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="B20" s="10"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="10"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="10"/>
+      <c r="B20" s="19"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="19"/>
     </row>
     <row r="21" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="16" t="s">
+      <c r="A21" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="B21" s="10"/>
-      <c r="C21" s="10"/>
-      <c r="D21" s="10"/>
-      <c r="E21" s="10"/>
-      <c r="F21" s="10"/>
+      <c r="B21" s="19"/>
+      <c r="C21" s="19"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="19"/>
+      <c r="F21" s="19"/>
     </row>
     <row r="22" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="12" t="s">
+      <c r="A22" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="B22" s="10"/>
-      <c r="C22" s="10"/>
-      <c r="D22" s="10"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="10"/>
+      <c r="B22" s="19"/>
+      <c r="C22" s="19"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="19"/>
+      <c r="F22" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="8">
